--- a/docs/heart_and_soul/Heart_and_Soul_checklist_test.xlsx
+++ b/docs/heart_and_soul/Heart_and_Soul_checklist_test.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Checklist" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Checklist'!$A$3:$F$101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Checklist'!$A$3:$F$103</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -646,19 +646,19 @@
     </row>
     <row r="6">
       <c r="B6" s="4">
-        <f>COUNTA(Checklist!A4:A101)</f>
+        <f>COUNTA(Checklist!A4:A103)</f>
         <v/>
       </c>
       <c r="C6" s="5">
-        <f>COUNTIF(Checklist!E4:E101,"OK")</f>
+        <f>COUNTIF(Checklist!E4:E103,"OK")</f>
         <v/>
       </c>
       <c r="D6" s="6">
-        <f>COUNTIF(Checklist!E4:E101,"KO")</f>
+        <f>COUNTIF(Checklist!E4:E103,"KO")</f>
         <v/>
       </c>
       <c r="E6" s="7">
-        <f>COUNTIF(Checklist!E4:E101,"Non testé")</f>
+        <f>COUNTIF(Checklist!E4:E103,"Non testé")</f>
         <v/>
       </c>
       <c r="F6" s="8">
@@ -707,19 +707,19 @@
         </is>
       </c>
       <c r="C10" s="12">
-        <f>COUNTIF(Checklist!B4:B101,B10)</f>
+        <f>COUNTIF(Checklist!B4:B103,B10)</f>
         <v/>
       </c>
       <c r="D10" s="12">
-        <f>COUNTIFS(Checklist!B4:B101,B10,Checklist!E4:E101,"OK")</f>
+        <f>COUNTIFS(Checklist!B4:B103,B10,Checklist!E4:E103,"OK")</f>
         <v/>
       </c>
       <c r="E10" s="12">
-        <f>COUNTIFS(Checklist!B4:B101,B10,Checklist!E4:E101,"KO")</f>
+        <f>COUNTIFS(Checklist!B4:B103,B10,Checklist!E4:E103,"KO")</f>
         <v/>
       </c>
       <c r="F10" s="12">
-        <f>COUNTIFS(Checklist!B4:B101,B10,Checklist!E4:E101,"Non testé")</f>
+        <f>COUNTIFS(Checklist!B4:B103,B10,Checklist!E4:E103,"Non testé")</f>
         <v/>
       </c>
     </row>
@@ -730,19 +730,19 @@
         </is>
       </c>
       <c r="C11" s="12">
-        <f>COUNTIF(Checklist!B4:B101,B11)</f>
+        <f>COUNTIF(Checklist!B4:B103,B11)</f>
         <v/>
       </c>
       <c r="D11" s="12">
-        <f>COUNTIFS(Checklist!B4:B101,B11,Checklist!E4:E101,"OK")</f>
+        <f>COUNTIFS(Checklist!B4:B103,B11,Checklist!E4:E103,"OK")</f>
         <v/>
       </c>
       <c r="E11" s="12">
-        <f>COUNTIFS(Checklist!B4:B101,B11,Checklist!E4:E101,"KO")</f>
+        <f>COUNTIFS(Checklist!B4:B103,B11,Checklist!E4:E103,"KO")</f>
         <v/>
       </c>
       <c r="F11" s="12">
-        <f>COUNTIFS(Checklist!B4:B101,B11,Checklist!E4:E101,"Non testé")</f>
+        <f>COUNTIFS(Checklist!B4:B103,B11,Checklist!E4:E103,"Non testé")</f>
         <v/>
       </c>
     </row>
@@ -753,19 +753,19 @@
         </is>
       </c>
       <c r="C12" s="12">
-        <f>COUNTIF(Checklist!B4:B101,B12)</f>
+        <f>COUNTIF(Checklist!B4:B103,B12)</f>
         <v/>
       </c>
       <c r="D12" s="12">
-        <f>COUNTIFS(Checklist!B4:B101,B12,Checklist!E4:E101,"OK")</f>
+        <f>COUNTIFS(Checklist!B4:B103,B12,Checklist!E4:E103,"OK")</f>
         <v/>
       </c>
       <c r="E12" s="12">
-        <f>COUNTIFS(Checklist!B4:B101,B12,Checklist!E4:E101,"KO")</f>
+        <f>COUNTIFS(Checklist!B4:B103,B12,Checklist!E4:E103,"KO")</f>
         <v/>
       </c>
       <c r="F12" s="12">
-        <f>COUNTIFS(Checklist!B4:B101,B12,Checklist!E4:E101,"Non testé")</f>
+        <f>COUNTIFS(Checklist!B4:B103,B12,Checklist!E4:E103,"Non testé")</f>
         <v/>
       </c>
     </row>
@@ -776,19 +776,19 @@
         </is>
       </c>
       <c r="C13" s="12">
-        <f>COUNTIF(Checklist!B4:B101,B13)</f>
+        <f>COUNTIF(Checklist!B4:B103,B13)</f>
         <v/>
       </c>
       <c r="D13" s="12">
-        <f>COUNTIFS(Checklist!B4:B101,B13,Checklist!E4:E101,"OK")</f>
+        <f>COUNTIFS(Checklist!B4:B103,B13,Checklist!E4:E103,"OK")</f>
         <v/>
       </c>
       <c r="E13" s="12">
-        <f>COUNTIFS(Checklist!B4:B101,B13,Checklist!E4:E101,"KO")</f>
+        <f>COUNTIFS(Checklist!B4:B103,B13,Checklist!E4:E103,"KO")</f>
         <v/>
       </c>
       <c r="F13" s="12">
-        <f>COUNTIFS(Checklist!B4:B101,B13,Checklist!E4:E101,"Non testé")</f>
+        <f>COUNTIFS(Checklist!B4:B103,B13,Checklist!E4:E103,"Non testé")</f>
         <v/>
       </c>
     </row>
@@ -799,19 +799,19 @@
         </is>
       </c>
       <c r="C14" s="12">
-        <f>COUNTIF(Checklist!B4:B101,B14)</f>
+        <f>COUNTIF(Checklist!B4:B103,B14)</f>
         <v/>
       </c>
       <c r="D14" s="12">
-        <f>COUNTIFS(Checklist!B4:B101,B14,Checklist!E4:E101,"OK")</f>
+        <f>COUNTIFS(Checklist!B4:B103,B14,Checklist!E4:E103,"OK")</f>
         <v/>
       </c>
       <c r="E14" s="12">
-        <f>COUNTIFS(Checklist!B4:B101,B14,Checklist!E4:E101,"KO")</f>
+        <f>COUNTIFS(Checklist!B4:B103,B14,Checklist!E4:E103,"KO")</f>
         <v/>
       </c>
       <c r="F14" s="12">
-        <f>COUNTIFS(Checklist!B4:B101,B14,Checklist!E4:E101,"Non testé")</f>
+        <f>COUNTIFS(Checklist!B4:B103,B14,Checklist!E4:E103,"Non testé")</f>
         <v/>
       </c>
     </row>
@@ -822,19 +822,19 @@
         </is>
       </c>
       <c r="C15" s="12">
-        <f>COUNTIF(Checklist!B4:B101,B15)</f>
+        <f>COUNTIF(Checklist!B4:B103,B15)</f>
         <v/>
       </c>
       <c r="D15" s="12">
-        <f>COUNTIFS(Checklist!B4:B101,B15,Checklist!E4:E101,"OK")</f>
+        <f>COUNTIFS(Checklist!B4:B103,B15,Checklist!E4:E103,"OK")</f>
         <v/>
       </c>
       <c r="E15" s="12">
-        <f>COUNTIFS(Checklist!B4:B101,B15,Checklist!E4:E101,"KO")</f>
+        <f>COUNTIFS(Checklist!B4:B103,B15,Checklist!E4:E103,"KO")</f>
         <v/>
       </c>
       <c r="F15" s="12">
-        <f>COUNTIFS(Checklist!B4:B101,B15,Checklist!E4:E101,"Non testé")</f>
+        <f>COUNTIFS(Checklist!B4:B103,B15,Checklist!E4:E103,"Non testé")</f>
         <v/>
       </c>
     </row>
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C16" s="12">
-        <f>COUNTIF(Checklist!B4:B101,B16)</f>
+        <f>COUNTIF(Checklist!B4:B103,B16)</f>
         <v/>
       </c>
       <c r="D16" s="12">
-        <f>COUNTIFS(Checklist!B4:B101,B16,Checklist!E4:E101,"OK")</f>
+        <f>COUNTIFS(Checklist!B4:B103,B16,Checklist!E4:E103,"OK")</f>
         <v/>
       </c>
       <c r="E16" s="12">
-        <f>COUNTIFS(Checklist!B4:B101,B16,Checklist!E4:E101,"KO")</f>
+        <f>COUNTIFS(Checklist!B4:B103,B16,Checklist!E4:E103,"KO")</f>
         <v/>
       </c>
       <c r="F16" s="12">
-        <f>COUNTIFS(Checklist!B4:B101,B16,Checklist!E4:E101,"Non testé")</f>
+        <f>COUNTIFS(Checklist!B4:B103,B16,Checklist!E4:E103,"Non testé")</f>
         <v/>
       </c>
     </row>
@@ -868,19 +868,19 @@
         </is>
       </c>
       <c r="C17" s="12">
-        <f>COUNTIF(Checklist!B4:B101,B17)</f>
+        <f>COUNTIF(Checklist!B4:B103,B17)</f>
         <v/>
       </c>
       <c r="D17" s="12">
-        <f>COUNTIFS(Checklist!B4:B101,B17,Checklist!E4:E101,"OK")</f>
+        <f>COUNTIFS(Checklist!B4:B103,B17,Checklist!E4:E103,"OK")</f>
         <v/>
       </c>
       <c r="E17" s="12">
-        <f>COUNTIFS(Checklist!B4:B101,B17,Checklist!E4:E101,"KO")</f>
+        <f>COUNTIFS(Checklist!B4:B103,B17,Checklist!E4:E103,"KO")</f>
         <v/>
       </c>
       <c r="F17" s="12">
-        <f>COUNTIFS(Checklist!B4:B101,B17,Checklist!E4:E101,"Non testé")</f>
+        <f>COUNTIFS(Checklist!B4:B103,B17,Checklist!E4:E103,"Non testé")</f>
         <v/>
       </c>
     </row>
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="C18" s="12">
-        <f>COUNTIF(Checklist!B4:B101,B18)</f>
+        <f>COUNTIF(Checklist!B4:B103,B18)</f>
         <v/>
       </c>
       <c r="D18" s="12">
-        <f>COUNTIFS(Checklist!B4:B101,B18,Checklist!E4:E101,"OK")</f>
+        <f>COUNTIFS(Checklist!B4:B103,B18,Checklist!E4:E103,"OK")</f>
         <v/>
       </c>
       <c r="E18" s="12">
-        <f>COUNTIFS(Checklist!B4:B101,B18,Checklist!E4:E101,"KO")</f>
+        <f>COUNTIFS(Checklist!B4:B103,B18,Checklist!E4:E103,"KO")</f>
         <v/>
       </c>
       <c r="F18" s="12">
-        <f>COUNTIFS(Checklist!B4:B101,B18,Checklist!E4:E101,"Non testé")</f>
+        <f>COUNTIFS(Checklist!B4:B103,B18,Checklist!E4:E103,"Non testé")</f>
         <v/>
       </c>
     </row>
@@ -914,19 +914,19 @@
         </is>
       </c>
       <c r="C19" s="12">
-        <f>COUNTIF(Checklist!B4:B101,B19)</f>
+        <f>COUNTIF(Checklist!B4:B103,B19)</f>
         <v/>
       </c>
       <c r="D19" s="12">
-        <f>COUNTIFS(Checklist!B4:B101,B19,Checklist!E4:E101,"OK")</f>
+        <f>COUNTIFS(Checklist!B4:B103,B19,Checklist!E4:E103,"OK")</f>
         <v/>
       </c>
       <c r="E19" s="12">
-        <f>COUNTIFS(Checklist!B4:B101,B19,Checklist!E4:E101,"KO")</f>
+        <f>COUNTIFS(Checklist!B4:B103,B19,Checklist!E4:E103,"KO")</f>
         <v/>
       </c>
       <c r="F19" s="12">
-        <f>COUNTIFS(Checklist!B4:B101,B19,Checklist!E4:E101,"Non testé")</f>
+        <f>COUNTIFS(Checklist!B4:B103,B19,Checklist!E4:E103,"Non testé")</f>
         <v/>
       </c>
     </row>
@@ -937,19 +937,19 @@
         </is>
       </c>
       <c r="C20" s="12">
-        <f>COUNTIF(Checklist!B4:B101,B20)</f>
+        <f>COUNTIF(Checklist!B4:B103,B20)</f>
         <v/>
       </c>
       <c r="D20" s="12">
-        <f>COUNTIFS(Checklist!B4:B101,B20,Checklist!E4:E101,"OK")</f>
+        <f>COUNTIFS(Checklist!B4:B103,B20,Checklist!E4:E103,"OK")</f>
         <v/>
       </c>
       <c r="E20" s="12">
-        <f>COUNTIFS(Checklist!B4:B101,B20,Checklist!E4:E101,"KO")</f>
+        <f>COUNTIFS(Checklist!B4:B103,B20,Checklist!E4:E103,"KO")</f>
         <v/>
       </c>
       <c r="F20" s="12">
-        <f>COUNTIFS(Checklist!B4:B101,B20,Checklist!E4:E101,"Non testé")</f>
+        <f>COUNTIFS(Checklist!B4:B103,B20,Checklist!E4:E103,"Non testé")</f>
         <v/>
       </c>
     </row>
@@ -960,19 +960,19 @@
         </is>
       </c>
       <c r="C21" s="12">
-        <f>COUNTIF(Checklist!B4:B101,B21)</f>
+        <f>COUNTIF(Checklist!B4:B103,B21)</f>
         <v/>
       </c>
       <c r="D21" s="12">
-        <f>COUNTIFS(Checklist!B4:B101,B21,Checklist!E4:E101,"OK")</f>
+        <f>COUNTIFS(Checklist!B4:B103,B21,Checklist!E4:E103,"OK")</f>
         <v/>
       </c>
       <c r="E21" s="12">
-        <f>COUNTIFS(Checklist!B4:B101,B21,Checklist!E4:E101,"KO")</f>
+        <f>COUNTIFS(Checklist!B4:B103,B21,Checklist!E4:E103,"KO")</f>
         <v/>
       </c>
       <c r="F21" s="12">
-        <f>COUNTIFS(Checklist!B4:B101,B21,Checklist!E4:E101,"Non testé")</f>
+        <f>COUNTIFS(Checklist!B4:B103,B21,Checklist!E4:E103,"Non testé")</f>
         <v/>
       </c>
     </row>
@@ -983,19 +983,19 @@
         </is>
       </c>
       <c r="C22" s="12">
-        <f>COUNTIF(Checklist!B4:B101,B22)</f>
+        <f>COUNTIF(Checklist!B4:B103,B22)</f>
         <v/>
       </c>
       <c r="D22" s="12">
-        <f>COUNTIFS(Checklist!B4:B101,B22,Checklist!E4:E101,"OK")</f>
+        <f>COUNTIFS(Checklist!B4:B103,B22,Checklist!E4:E103,"OK")</f>
         <v/>
       </c>
       <c r="E22" s="12">
-        <f>COUNTIFS(Checklist!B4:B101,B22,Checklist!E4:E101,"KO")</f>
+        <f>COUNTIFS(Checklist!B4:B103,B22,Checklist!E4:E103,"KO")</f>
         <v/>
       </c>
       <c r="F22" s="12">
-        <f>COUNTIFS(Checklist!B4:B101,B22,Checklist!E4:E101,"Non testé")</f>
+        <f>COUNTIFS(Checklist!B4:B103,B22,Checklist!E4:E103,"Non testé")</f>
         <v/>
       </c>
     </row>
@@ -1006,19 +1006,19 @@
         </is>
       </c>
       <c r="C23" s="12">
-        <f>COUNTIF(Checklist!B4:B101,B23)</f>
+        <f>COUNTIF(Checklist!B4:B103,B23)</f>
         <v/>
       </c>
       <c r="D23" s="12">
-        <f>COUNTIFS(Checklist!B4:B101,B23,Checklist!E4:E101,"OK")</f>
+        <f>COUNTIFS(Checklist!B4:B103,B23,Checklist!E4:E103,"OK")</f>
         <v/>
       </c>
       <c r="E23" s="12">
-        <f>COUNTIFS(Checklist!B4:B101,B23,Checklist!E4:E101,"KO")</f>
+        <f>COUNTIFS(Checklist!B4:B103,B23,Checklist!E4:E103,"KO")</f>
         <v/>
       </c>
       <c r="F23" s="12">
-        <f>COUNTIFS(Checklist!B4:B101,B23,Checklist!E4:E101,"Non testé")</f>
+        <f>COUNTIFS(Checklist!B4:B103,B23,Checklist!E4:E103,"Non testé")</f>
         <v/>
       </c>
     </row>
@@ -1029,19 +1029,19 @@
         </is>
       </c>
       <c r="C24" s="12">
-        <f>COUNTIF(Checklist!B4:B101,B24)</f>
+        <f>COUNTIF(Checklist!B4:B103,B24)</f>
         <v/>
       </c>
       <c r="D24" s="12">
-        <f>COUNTIFS(Checklist!B4:B101,B24,Checklist!E4:E101,"OK")</f>
+        <f>COUNTIFS(Checklist!B4:B103,B24,Checklist!E4:E103,"OK")</f>
         <v/>
       </c>
       <c r="E24" s="12">
-        <f>COUNTIFS(Checklist!B4:B101,B24,Checklist!E4:E101,"KO")</f>
+        <f>COUNTIFS(Checklist!B4:B103,B24,Checklist!E4:E103,"KO")</f>
         <v/>
       </c>
       <c r="F24" s="12">
-        <f>COUNTIFS(Checklist!B4:B101,B24,Checklist!E4:E101,"Non testé")</f>
+        <f>COUNTIFS(Checklist!B4:B103,B24,Checklist!E4:E103,"Non testé")</f>
         <v/>
       </c>
     </row>
@@ -1052,19 +1052,19 @@
         </is>
       </c>
       <c r="C25" s="12">
-        <f>COUNTIF(Checklist!B4:B101,B25)</f>
+        <f>COUNTIF(Checklist!B4:B103,B25)</f>
         <v/>
       </c>
       <c r="D25" s="12">
-        <f>COUNTIFS(Checklist!B4:B101,B25,Checklist!E4:E101,"OK")</f>
+        <f>COUNTIFS(Checklist!B4:B103,B25,Checklist!E4:E103,"OK")</f>
         <v/>
       </c>
       <c r="E25" s="12">
-        <f>COUNTIFS(Checklist!B4:B101,B25,Checklist!E4:E101,"KO")</f>
+        <f>COUNTIFS(Checklist!B4:B103,B25,Checklist!E4:E103,"KO")</f>
         <v/>
       </c>
       <c r="F25" s="12">
-        <f>COUNTIFS(Checklist!B4:B101,B25,Checklist!E4:E101,"Non testé")</f>
+        <f>COUNTIFS(Checklist!B4:B103,B25,Checklist!E4:E103,"Non testé")</f>
         <v/>
       </c>
     </row>
@@ -1075,19 +1075,19 @@
         </is>
       </c>
       <c r="C26" s="12">
-        <f>COUNTIF(Checklist!B4:B101,B26)</f>
+        <f>COUNTIF(Checklist!B4:B103,B26)</f>
         <v/>
       </c>
       <c r="D26" s="12">
-        <f>COUNTIFS(Checklist!B4:B101,B26,Checklist!E4:E101,"OK")</f>
+        <f>COUNTIFS(Checklist!B4:B103,B26,Checklist!E4:E103,"OK")</f>
         <v/>
       </c>
       <c r="E26" s="12">
-        <f>COUNTIFS(Checklist!B4:B101,B26,Checklist!E4:E101,"KO")</f>
+        <f>COUNTIFS(Checklist!B4:B103,B26,Checklist!E4:E103,"KO")</f>
         <v/>
       </c>
       <c r="F26" s="12">
-        <f>COUNTIFS(Checklist!B4:B101,B26,Checklist!E4:E101,"Non testé")</f>
+        <f>COUNTIFS(Checklist!B4:B103,B26,Checklist!E4:E103,"Non testé")</f>
         <v/>
       </c>
     </row>
@@ -1098,19 +1098,19 @@
         </is>
       </c>
       <c r="C27" s="12">
-        <f>COUNTIF(Checklist!B4:B101,B27)</f>
+        <f>COUNTIF(Checklist!B4:B103,B27)</f>
         <v/>
       </c>
       <c r="D27" s="12">
-        <f>COUNTIFS(Checklist!B4:B101,B27,Checklist!E4:E101,"OK")</f>
+        <f>COUNTIFS(Checklist!B4:B103,B27,Checklist!E4:E103,"OK")</f>
         <v/>
       </c>
       <c r="E27" s="12">
-        <f>COUNTIFS(Checklist!B4:B101,B27,Checklist!E4:E101,"KO")</f>
+        <f>COUNTIFS(Checklist!B4:B103,B27,Checklist!E4:E103,"KO")</f>
         <v/>
       </c>
       <c r="F27" s="12">
-        <f>COUNTIFS(Checklist!B4:B101,B27,Checklist!E4:E101,"Non testé")</f>
+        <f>COUNTIFS(Checklist!B4:B103,B27,Checklist!E4:E103,"Non testé")</f>
         <v/>
       </c>
     </row>
@@ -1121,19 +1121,19 @@
         </is>
       </c>
       <c r="C28" s="12">
-        <f>COUNTIF(Checklist!B4:B101,B28)</f>
+        <f>COUNTIF(Checklist!B4:B103,B28)</f>
         <v/>
       </c>
       <c r="D28" s="12">
-        <f>COUNTIFS(Checklist!B4:B101,B28,Checklist!E4:E101,"OK")</f>
+        <f>COUNTIFS(Checklist!B4:B103,B28,Checklist!E4:E103,"OK")</f>
         <v/>
       </c>
       <c r="E28" s="12">
-        <f>COUNTIFS(Checklist!B4:B101,B28,Checklist!E4:E101,"KO")</f>
+        <f>COUNTIFS(Checklist!B4:B103,B28,Checklist!E4:E103,"KO")</f>
         <v/>
       </c>
       <c r="F28" s="12">
-        <f>COUNTIFS(Checklist!B4:B101,B28,Checklist!E4:E101,"Non testé")</f>
+        <f>COUNTIFS(Checklist!B4:B103,B28,Checklist!E4:E103,"Non testé")</f>
         <v/>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F101"/>
+  <dimension ref="A1:F103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1507,10 +1507,14 @@
       </c>
       <c r="C16" s="17" t="inlineStr">
         <is>
-          <t>Narration de l'attaque, un Grunt fait irruption, Blaine s'interpose puis disparaît (texte uniquement, pas de sprite visible à ce moment).</t>
-        </is>
-      </c>
-      <c r="D16" s="18" t="inlineStr"/>
+          <t>PRIORITAIRE (nouveau) : après le premier message d'alarme, un fondu au noir doit téléporter automatiquement sur la carte extérieure de Cinnabar (près de Blaine), pas rester dans le Centre Pokémon. Si l'écran reste noir/se bloque/plante ici, c'est le point exact à signaler.</t>
+        </is>
+      </c>
+      <c r="D16" s="18" t="inlineStr">
+        <is>
+          <t>PRIORITAIRE</t>
+        </is>
+      </c>
       <c r="E16" s="16" t="inlineStr">
         <is>
           <t>Non testé</t>
@@ -1529,12 +1533,12 @@
       </c>
       <c r="C17" s="17" t="inlineStr">
         <is>
-          <t>Un second Grunt bloque le passage juste après : combat forcé (pas de choix, pas de fuite possible), équipe niveau ~34. Après la victoire, le texte confirme que le passage vers le Mont Cinnabar est libre.</t>
+          <t>Une fois dehors : un Grunt entre visiblement en marchant vers Blaine, Blaine réagit (exclamation) puis se place entre le Grunt et le joueur, le joueur recule d'une case — tout doit être visible à l'écran, pas seulement raconté.</t>
         </is>
       </c>
       <c r="D17" s="18" t="inlineStr">
         <is>
-          <t>Un second Grunt bloque le passage juste après</t>
+          <t>Une fois dehors</t>
         </is>
       </c>
       <c r="E17" s="16" t="inlineStr">
@@ -1555,12 +1559,12 @@
       </c>
       <c r="C18" s="17" t="inlineStr">
         <is>
-          <t>Choix réfugiés (guider / cacher) : les deux options fonctionnent, message de résultat cohérent.</t>
+          <t>Après le flash/l'impact : fondu au noir, Blaine disparaît (son sprite n'est plus là au fondu suivant).</t>
         </is>
       </c>
       <c r="D18" s="18" t="inlineStr">
         <is>
-          <t>Choix réfugiés</t>
+          <t>Après le flash/l'impact</t>
         </is>
       </c>
       <c r="E18" s="16" t="inlineStr">
@@ -1581,7 +1585,7 @@
       </c>
       <c r="C19" s="17" t="inlineStr">
         <is>
-          <t>Message de fuite → fondu au noir → téléportation automatique à Pallet Town, sans avoir à marcher ni utiliser un CS Fly.</t>
+          <t>Le même Grunt se retourne vers le joueur et lance un combat forcé (pas de choix, pas de fuite possible), équipe niveau ~34. Après la victoire, le texte confirme que le passage vers le Mont Cinnabar est libre et le Grunt disparaît.</t>
         </is>
       </c>
       <c r="D19" s="18" t="inlineStr"/>
@@ -1603,12 +1607,12 @@
       </c>
       <c r="C20" s="17" t="inlineStr">
         <is>
-          <t>Essayer de retourner vers Cinnabar (Route 21, vers le sud) : le jeu doit repousser le joueur avec un message, pas de possibilité d'entrer.</t>
+          <t>Choix réfugiés (guider / cacher) : les deux options fonctionnent, message de résultat cohérent.</t>
         </is>
       </c>
       <c r="D20" s="18" t="inlineStr">
         <is>
-          <t>Essayer de retourner vers Cinnabar</t>
+          <t>Choix réfugiés</t>
         </is>
       </c>
       <c r="E20" s="16" t="inlineStr">
@@ -1624,12 +1628,12 @@
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>4. Route 1</t>
+          <t>3. Attaque de Cinnabar (Acte I)</t>
         </is>
       </c>
       <c r="C21" s="17" t="inlineStr">
         <is>
-          <t>Combattre Quinn (Cooltrainer F).</t>
+          <t>Message de fuite → fondu au noir → téléportation automatique à Pallet Town, sans avoir à marcher ni utiliser un CS Fly.</t>
         </is>
       </c>
       <c r="D21" s="18" t="inlineStr"/>
@@ -1646,17 +1650,17 @@
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>4. Route 1</t>
+          <t>3. Attaque de Cinnabar (Acte I)</t>
         </is>
       </c>
       <c r="C22" s="17" t="inlineStr">
         <is>
-          <t>Juste après la victoire, sans avoir à lui reparler : dialogue de post-combat puis proposition de rendre le bracelet trouvé à Cinnabar.</t>
+          <t>Essayer de retourner vers Cinnabar (Route 21, vers le sud) : le jeu doit repousser le joueur avec un message, pas de possibilité d'entrer.</t>
         </is>
       </c>
       <c r="D22" s="18" t="inlineStr">
         <is>
-          <t>Juste après la victoire, sans avoir à lui reparler</t>
+          <t>Essayer de retourner vers Cinnabar</t>
         </is>
       </c>
       <c r="E22" s="16" t="inlineStr">
@@ -1677,7 +1681,7 @@
       </c>
       <c r="C23" s="17" t="inlineStr">
         <is>
-          <t>Tester les deux choix (rendre / garder) sur des essais différents si possible.</t>
+          <t>Combattre Quinn (Cooltrainer F).</t>
         </is>
       </c>
       <c r="D23" s="18" t="inlineStr"/>
@@ -1694,17 +1698,17 @@
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>5. Viridian (Argenta)</t>
+          <t>4. Route 1</t>
         </is>
       </c>
       <c r="C24" s="17" t="inlineStr">
         <is>
-          <t>Mart : parler au PNJ (ex-« Cooltrainer M ») → proposition de rejoindre la résistance, choix aider/décliner fonctionnent.</t>
+          <t>Juste après la victoire, sans avoir à lui reparler : dialogue de post-combat puis proposition de rendre le bracelet trouvé à Cinnabar.</t>
         </is>
       </c>
       <c r="D24" s="18" t="inlineStr">
         <is>
-          <t>Mart</t>
+          <t>Juste après la victoire, sans avoir à lui reparler</t>
         </is>
       </c>
       <c r="E24" s="16" t="inlineStr">
@@ -1720,19 +1724,15 @@
       </c>
       <c r="B25" s="17" t="inlineStr">
         <is>
-          <t>5. Viridian (Argenta)</t>
+          <t>4. Route 1</t>
         </is>
       </c>
       <c r="C25" s="17" t="inlineStr">
         <is>
-          <t>Mart : parler au vendeur (comptoir) → un vrai magasin s'ouvre avec Poké Ball/Potion/Antidote/Anti-Paralysie à acheter.</t>
-        </is>
-      </c>
-      <c r="D25" s="18" t="inlineStr">
-        <is>
-          <t>Mart</t>
-        </is>
-      </c>
+          <t>Tester les deux choix (rendre / garder) sur des essais différents si possible.</t>
+        </is>
+      </c>
+      <c r="D25" s="18" t="inlineStr"/>
       <c r="E25" s="16" t="inlineStr">
         <is>
           <t>Non testé</t>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="C26" s="17" t="inlineStr">
         <is>
-          <t>Arène : Blue est absent, le PNJ à l'intérieur explique que l'Arène est fermée (pas de combat possible).</t>
+          <t>Mart : parler au PNJ (ex-« Cooltrainer M ») → proposition de rejoindre la résistance, choix aider/décliner fonctionnent.</t>
         </is>
       </c>
       <c r="D26" s="18" t="inlineStr">
         <is>
-          <t>Arène</t>
+          <t>Mart</t>
         </is>
       </c>
       <c r="E26" s="16" t="inlineStr">
@@ -1772,15 +1772,19 @@
       </c>
       <c r="B27" s="17" t="inlineStr">
         <is>
-          <t>6. Forêt de Jade (Viridian Forest)</t>
+          <t>5. Viridian (Argenta)</t>
         </is>
       </c>
       <c r="C27" s="17" t="inlineStr">
         <is>
-          <t>Combattre Doug (Bug Catcher) — il erre assez loin de l'entrée nord, plutôt vers le centre-sud de la forêt, proche de la sortie côté Jadielle/Pewter. Continuer vers le sud si non trouvé près de l'entrée.</t>
-        </is>
-      </c>
-      <c r="D27" s="18" t="inlineStr"/>
+          <t>Mart : parler au vendeur (comptoir) → un vrai magasin s'ouvre avec Poké Ball/Potion/Antidote/Anti-Paralysie à acheter.</t>
+        </is>
+      </c>
+      <c r="D27" s="18" t="inlineStr">
+        <is>
+          <t>Mart</t>
+        </is>
+      </c>
       <c r="E27" s="16" t="inlineStr">
         <is>
           <t>Non testé</t>
@@ -1794,17 +1798,17 @@
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>6. Forêt de Jade (Viridian Forest)</t>
+          <t>5. Viridian (Argenta)</t>
         </is>
       </c>
       <c r="C28" s="17" t="inlineStr">
         <is>
-          <t>Juste après la victoire, sans avoir à lui reparler : dialogue bûcherons déplacés, choix aider/ignorer fonctionnent.</t>
+          <t>Arène : Blue est absent, le PNJ à l'intérieur explique que l'Arène est fermée (pas de combat possible).</t>
         </is>
       </c>
       <c r="D28" s="18" t="inlineStr">
         <is>
-          <t>Juste après la victoire, sans avoir à lui reparler</t>
+          <t>Arène</t>
         </is>
       </c>
       <c r="E28" s="16" t="inlineStr">
@@ -1820,12 +1824,12 @@
       </c>
       <c r="B29" s="17" t="inlineStr">
         <is>
-          <t>7. Argenta → Jadielle → Azuria (route et niveaux)</t>
+          <t>6. Forêt de Jade (Viridian Forest)</t>
         </is>
       </c>
       <c r="C29" s="17" t="inlineStr">
         <is>
-          <t>Pokémon sauvages rencontrés sur Route 1/2/3/4, Forêt de Jade, Mont Sélénite : niveau ~34 (pas 45+).</t>
+          <t>Combattre Doug (Bug Catcher) — il erre assez loin de l'entrée nord, plutôt vers le centre-sud de la forêt, proche de la sortie côté Jadielle/Pewter. Continuer vers le sud si non trouvé près de l'entrée.</t>
         </is>
       </c>
       <c r="D29" s="18" t="inlineStr"/>
@@ -1842,17 +1846,17 @@
       </c>
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>7. Argenta → Jadielle → Azuria (route et niveaux)</t>
+          <t>6. Forêt de Jade (Viridian Forest)</t>
         </is>
       </c>
       <c r="C30" s="17" t="inlineStr">
         <is>
-          <t>Dresseurs rencontrés sur la route (Danny, Ed, Rob, etc.) : niveau ~34.</t>
+          <t>Juste après la victoire, sans avoir à lui reparler : dialogue bûcherons déplacés, choix aider/ignorer fonctionnent.</t>
         </is>
       </c>
       <c r="D30" s="18" t="inlineStr">
         <is>
-          <t>Dresseurs rencontrés sur la route</t>
+          <t>Juste après la victoire, sans avoir à lui reparler</t>
         </is>
       </c>
       <c r="E30" s="16" t="inlineStr">
@@ -1873,7 +1877,7 @@
       </c>
       <c r="C31" s="17" t="inlineStr">
         <is>
-          <t>Coupe/Surf/Vol/Force/etc. utilisable sans badge depuis le menu Pokémon (CT + Pokémon compatible fournis dès le départ, voir section 2).</t>
+          <t>Pokémon sauvages rencontrés sur Route 1/2/3/4, Forêt de Jade, Mont Sélénite : niveau ~34 (pas 45+).</t>
         </is>
       </c>
       <c r="D31" s="18" t="inlineStr"/>
@@ -1890,17 +1894,17 @@
       </c>
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>8. Arène de Pierre (Jadielle)</t>
+          <t>7. Argenta → Jadielle → Azuria (route et niveaux)</t>
         </is>
       </c>
       <c r="C32" s="17" t="inlineStr">
         <is>
-          <t>Mart de Jadielle : le vendeur au comptoir vend Poké Ball/Potion/Antidote/Anti-Paralysie/Réveil/Anti-Brûlure/Corde Sortie/Repousse.</t>
+          <t>Dresseurs rencontrés sur la route (Danny, Ed, Rob, etc.) : niveau ~34.</t>
         </is>
       </c>
       <c r="D32" s="18" t="inlineStr">
         <is>
-          <t>Mart de Jadielle</t>
+          <t>Dresseurs rencontrés sur la route</t>
         </is>
       </c>
       <c r="E32" s="16" t="inlineStr">
@@ -1916,19 +1920,15 @@
       </c>
       <c r="B33" s="17" t="inlineStr">
         <is>
-          <t>8. Arène de Pierre (Jadielle)</t>
+          <t>7. Argenta → Jadielle → Azuria (route et niveaux)</t>
         </is>
       </c>
       <c r="C33" s="17" t="inlineStr">
         <is>
-          <t>En arrivant à l'Arène : seul notre dialogue (Pierre doute) s'affiche, puis le combat démarre directement — plus de texte anglais générique avant le combat.</t>
-        </is>
-      </c>
-      <c r="D33" s="18" t="inlineStr">
-        <is>
-          <t>En arrivant à l'Arène</t>
-        </is>
-      </c>
+          <t>Coupe/Surf/Vol/Force/etc. utilisable sans badge depuis le menu Pokémon (CT + Pokémon compatible fournis dès le départ, voir section 2).</t>
+        </is>
+      </c>
+      <c r="D33" s="18" t="inlineStr"/>
       <c r="E33" s="16" t="inlineStr">
         <is>
           <t>Non testé</t>
@@ -1947,10 +1947,14 @@
       </c>
       <c r="C34" s="17" t="inlineStr">
         <is>
-          <t>Perdre volontairement ce premier combat, puis reparler à Pierre : la scène de doute (en français) doit se rejouer.</t>
-        </is>
-      </c>
-      <c r="D34" s="18" t="inlineStr"/>
+          <t>Mart de Jadielle : le vendeur au comptoir vend Poké Ball/Potion/Antidote/Anti-Paralysie/Réveil/Anti-Brûlure/Corde Sortie/Repousse.</t>
+        </is>
+      </c>
+      <c r="D34" s="18" t="inlineStr">
+        <is>
+          <t>Mart de Jadielle</t>
+        </is>
+      </c>
       <c r="E34" s="16" t="inlineStr">
         <is>
           <t>Non testé</t>
@@ -1969,12 +1973,12 @@
       </c>
       <c r="C35" s="17" t="inlineStr">
         <is>
-          <t>Gagner le combat : badge + CT Éboulement reçus normalement, puis un nouveau texte (en français, lié à notre histoire) où Pierre reconnaît avoir été convaincu.</t>
+          <t>En arrivant à l'Arène : seul notre dialogue (Pierre doute) s'affiche, puis le combat démarre directement — plus de texte anglais générique avant le combat.</t>
         </is>
       </c>
       <c r="D35" s="18" t="inlineStr">
         <is>
-          <t>Gagner le combat</t>
+          <t>En arrivant à l'Arène</t>
         </is>
       </c>
       <c r="E35" s="16" t="inlineStr">
@@ -1990,19 +1994,15 @@
       </c>
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>9. Azuria</t>
+          <t>8. Arène de Pierre (Jadielle)</t>
         </is>
       </c>
       <c r="C36" s="17" t="inlineStr">
         <is>
-          <t>Mart d'Azuria : le vendeur vend en plus une Super Potion.</t>
-        </is>
-      </c>
-      <c r="D36" s="18" t="inlineStr">
-        <is>
-          <t>Mart d'Azuria</t>
-        </is>
-      </c>
+          <t>Perdre volontairement ce premier combat, puis reparler à Pierre : la scène de doute (en français) doit se rejouer.</t>
+        </is>
+      </c>
+      <c r="D36" s="18" t="inlineStr"/>
       <c r="E36" s="16" t="inlineStr">
         <is>
           <t>Non testé</t>
@@ -2016,17 +2016,17 @@
       </c>
       <c r="B37" s="17" t="inlineStr">
         <is>
-          <t>9. Azuria</t>
+          <t>8. Arène de Pierre (Jadielle)</t>
         </is>
       </c>
       <c r="C37" s="17" t="inlineStr">
         <is>
-          <t>Avant de réparer les canalisations : à l'Arène, Ondine explique le problème (Arène inondée/bloquée) et dit qu'elle n'écoutera qu'une fois les canalisations réparées — pas de combat possible à ce stade.</t>
+          <t>Gagner le combat : badge + CT Éboulement reçus normalement, puis un nouveau texte (en français, lié à notre histoire) où Pierre reconnaît avoir été convaincu.</t>
         </is>
       </c>
       <c r="D37" s="18" t="inlineStr">
         <is>
-          <t>Avant de réparer les canalisations</t>
+          <t>Gagner le combat</t>
         </is>
       </c>
       <c r="E37" s="16" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="C38" s="17" t="inlineStr">
         <is>
-          <t>Toujours avant réparation : un PNJ Team Rocket est présent et interactif dans l'Arène (parler à lui affiche une ligne de sabotage).</t>
+          <t>Mart d'Azuria : le vendeur vend en plus une Super Potion.</t>
         </is>
       </c>
       <c r="D38" s="18" t="inlineStr">
         <is>
-          <t>Toujours avant réparation</t>
+          <t>Mart d'Azuria</t>
         </is>
       </c>
       <c r="E38" s="16" t="inlineStr">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="C39" s="17" t="inlineStr">
         <is>
-          <t>PNJ « canalisations sabotées » (Boy, en ville) : choix aider/ignorer fonctionnent, réparation obtenue.</t>
+          <t>Avant de réparer les canalisations : à l'Arène, Ondine explique le problème (Arène inondée/bloquée) et dit qu'elle n'écoutera qu'une fois les canalisations réparées — pas de combat possible à ce stade.</t>
         </is>
       </c>
       <c r="D39" s="18" t="inlineStr">
         <is>
-          <t>PNJ « canalisations sabotées »</t>
+          <t>Avant de réparer les canalisations</t>
         </is>
       </c>
       <c r="E39" s="16" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="C40" s="17" t="inlineStr">
         <is>
-          <t>Après réparation des canalisations : retourner à l'Arène — le PNJ Rocket a disparu, le combat contre Ondine est maintenant possible (notre dialogue, puis le combat) ; en cas de défaite, la scène se rejoue à la tentative suivante.</t>
+          <t>Toujours avant réparation : un PNJ Team Rocket est présent et interactif dans l'Arène (parler à lui affiche une ligne de sabotage).</t>
         </is>
       </c>
       <c r="D40" s="18" t="inlineStr">
         <is>
-          <t>Après réparation des canalisations</t>
+          <t>Toujours avant réparation</t>
         </is>
       </c>
       <c r="E40" s="16" t="inlineStr">
@@ -2120,15 +2120,19 @@
       </c>
       <c r="B41" s="17" t="inlineStr">
         <is>
-          <t>10. Route vers Carmin-sur-Mer (Vermilion)</t>
+          <t>9. Azuria</t>
         </is>
       </c>
       <c r="C41" s="17" t="inlineStr">
         <is>
-          <t>Depuis Azuria, prendre la route vers le nord (Route 5) → traverser Safrania (simple passage, pas d'arène ici) → Route 6 → Carmin-sur-Mer. Aucun garde ne doit bloquer ce trajet.</t>
-        </is>
-      </c>
-      <c r="D41" s="18" t="inlineStr"/>
+          <t>PNJ « canalisations sabotées » (Boy, en ville) : choix aider/ignorer fonctionnent, réparation obtenue.</t>
+        </is>
+      </c>
+      <c r="D41" s="18" t="inlineStr">
+        <is>
+          <t>PNJ « canalisations sabotées »</t>
+        </is>
+      </c>
       <c r="E41" s="16" t="inlineStr">
         <is>
           <t>Non testé</t>
@@ -2142,17 +2146,17 @@
       </c>
       <c r="B42" s="17" t="inlineStr">
         <is>
-          <t>10. Route vers Carmin-sur-Mer (Vermilion)</t>
+          <t>9. Azuria</t>
         </is>
       </c>
       <c r="C42" s="17" t="inlineStr">
         <is>
-          <t>Dresseurs et Pokémon sauvages sur ce trajet : niveau ~34.</t>
+          <t>Après réparation des canalisations : retourner à l'Arène — le PNJ Rocket a disparu, le combat contre Ondine est maintenant possible (notre dialogue, puis le combat) ; en cas de défaite, la scène se rejoue à la tentative suivante.</t>
         </is>
       </c>
       <c r="D42" s="18" t="inlineStr">
         <is>
-          <t>Dresseurs et Pokémon sauvages sur ce trajet</t>
+          <t>Après réparation des canalisations</t>
         </is>
       </c>
       <c r="E42" s="16" t="inlineStr">
@@ -2173,14 +2177,10 @@
       </c>
       <c r="C43" s="17" t="inlineStr">
         <is>
-          <t>À Carmin-sur-Mer : parler au PNJ « Nerd » (interception radio) → choix aider/ignorer fonctionnent.</t>
-        </is>
-      </c>
-      <c r="D43" s="18" t="inlineStr">
-        <is>
-          <t>À Carmin-sur-Mer</t>
-        </is>
-      </c>
+          <t>Depuis Azuria, prendre la route vers le nord (Route 5) → traverser Safrania (simple passage, pas d'arène ici) → Route 6 → Carmin-sur-Mer. Aucun garde ne doit bloquer ce trajet.</t>
+        </is>
+      </c>
+      <c r="D43" s="18" t="inlineStr"/>
       <c r="E43" s="16" t="inlineStr">
         <is>
           <t>Non testé</t>
@@ -2199,12 +2199,12 @@
       </c>
       <c r="C44" s="17" t="inlineStr">
         <is>
-          <t>Mart de Carmin-sur-Mer : le vendeur vend Poké Ball/Super Potion/Antidote/Anti-Paralysie/Réveil/Anti-Gel/Repousse.</t>
+          <t>Dresseurs et Pokémon sauvages sur ce trajet : niveau ~34.</t>
         </is>
       </c>
       <c r="D44" s="18" t="inlineStr">
         <is>
-          <t>Mart de Carmin-sur-Mer</t>
+          <t>Dresseurs et Pokémon sauvages sur ce trajet</t>
         </is>
       </c>
       <c r="E44" s="16" t="inlineStr">
@@ -2220,17 +2220,17 @@
       </c>
       <c r="B45" s="17" t="inlineStr">
         <is>
-          <t>11. Arène de Major Bob (Carmin-sur-Mer, 4e arène)</t>
+          <t>10. Route vers Carmin-sur-Mer (Vermilion)</t>
         </is>
       </c>
       <c r="C45" s="17" t="inlineStr">
         <is>
-          <t>Même schéma que Pierre/Ondine : notre dialogue (Major Bob doute), puis l'anglais, puis le combat.</t>
+          <t>À Carmin-sur-Mer : parler au PNJ « Nerd » (interception radio) → choix aider/ignorer fonctionnent.</t>
         </is>
       </c>
       <c r="D45" s="18" t="inlineStr">
         <is>
-          <t>Même schéma que Pierre/Ondine</t>
+          <t>À Carmin-sur-Mer</t>
         </is>
       </c>
       <c r="E45" s="16" t="inlineStr">
@@ -2246,17 +2246,17 @@
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
-          <t>11. Arène de Major Bob (Carmin-sur-Mer, 4e arène)</t>
+          <t>10. Route vers Carmin-sur-Mer (Vermilion)</t>
         </is>
       </c>
       <c r="C46" s="17" t="inlineStr">
         <is>
-          <t>Perdre volontairement puis retenter : la scène de doute se rejoue.</t>
+          <t>Mart de Carmin-sur-Mer : le vendeur vend Poké Ball/Super Potion/Antidote/Anti-Paralysie/Réveil/Anti-Gel/Repousse.</t>
         </is>
       </c>
       <c r="D46" s="18" t="inlineStr">
         <is>
-          <t>Perdre volontairement puis retenter</t>
+          <t>Mart de Carmin-sur-Mer</t>
         </is>
       </c>
       <c r="E46" s="16" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="C47" s="17" t="inlineStr">
         <is>
-          <t>Gagner : badge reçu normalement.</t>
+          <t>Même schéma que Pierre/Ondine : notre dialogue (Major Bob doute), puis l'anglais, puis le combat.</t>
         </is>
       </c>
       <c r="D47" s="18" t="inlineStr">
         <is>
-          <t>Gagner</t>
+          <t>Même schéma que Pierre/Ondine</t>
         </is>
       </c>
       <c r="E47" s="16" t="inlineStr">
@@ -2298,17 +2298,17 @@
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>12. Portes de Cinnabar (Arène/Manoir/Labo) — build séparé</t>
+          <t>11. Arène de Major Bob (Carmin-sur-Mer, 4e arène)</t>
         </is>
       </c>
       <c r="C48" s="17" t="inlineStr">
         <is>
-          <t>Ce test ne se fait pas dans la partie normale : lancer make hns MAPTEST=1 (voir MAP_TEST_README.md à la racine du dépôt) pour une ROM dédiée qui démarre directement à côté des 3 portes sur CinnabarIsland_hns.</t>
+          <t>Perdre volontairement puis retenter : la scène de doute se rejoue.</t>
         </is>
       </c>
       <c r="D48" s="18" t="inlineStr">
         <is>
-          <t>Ce test ne se fait pas dans la partie normale</t>
+          <t>Perdre volontairement puis retenter</t>
         </is>
       </c>
       <c r="E48" s="16" t="inlineStr">
@@ -2324,15 +2324,19 @@
       </c>
       <c r="B49" s="17" t="inlineStr">
         <is>
-          <t>12. Portes de Cinnabar (Arène/Manoir/Labo) — build séparé</t>
+          <t>11. Arène de Major Bob (Carmin-sur-Mer, 4e arène)</t>
         </is>
       </c>
       <c r="C49" s="17" t="inlineStr">
         <is>
-          <t>Les 3 portes (Arène, Manoir, Labo) sont visibles et franchissables, chacune mène au bon intérieur.</t>
-        </is>
-      </c>
-      <c r="D49" s="18" t="inlineStr"/>
+          <t>Gagner : badge reçu normalement.</t>
+        </is>
+      </c>
+      <c r="D49" s="18" t="inlineStr">
+        <is>
+          <t>Gagner</t>
+        </is>
+      </c>
       <c r="E49" s="16" t="inlineStr">
         <is>
           <t>Non testé</t>
@@ -2351,10 +2355,14 @@
       </c>
       <c r="C50" s="17" t="inlineStr">
         <is>
-          <t>Sortir de chaque bâtiment ramène bien sur Cinnabar (pas sur l'ancien Kanto inerte).</t>
-        </is>
-      </c>
-      <c r="D50" s="18" t="inlineStr"/>
+          <t>Ce test ne se fait pas dans la partie normale : lancer make hns MAPTEST=1 (voir MAP_TEST_README.md à la racine du dépôt) pour une ROM dédiée qui démarre directement à côté des 3 portes sur CinnabarIsland_hns.</t>
+        </is>
+      </c>
+      <c r="D50" s="18" t="inlineStr">
+        <is>
+          <t>Ce test ne se fait pas dans la partie normale</t>
+        </is>
+      </c>
       <c r="E50" s="16" t="inlineStr">
         <is>
           <t>Non testé</t>
@@ -2373,14 +2381,10 @@
       </c>
       <c r="C51" s="17" t="inlineStr">
         <is>
-          <t>Ne pas entrer dans le Centre Pokémon dans ce build de test : ça déclenche le script d'attaque de l'Acte I, hors périmètre de ce test précis.</t>
-        </is>
-      </c>
-      <c r="D51" s="18" t="inlineStr">
-        <is>
-          <t>Ne pas entrer dans le Centre Pokémon dans ce build de test</t>
-        </is>
-      </c>
+          <t>Les 3 portes (Arène, Manoir, Labo) sont visibles et franchissables, chacune mène au bon intérieur.</t>
+        </is>
+      </c>
+      <c r="D51" s="18" t="inlineStr"/>
       <c r="E51" s="16" t="inlineStr">
         <is>
           <t>Non testé</t>
@@ -2399,14 +2403,10 @@
       </c>
       <c r="C52" s="17" t="inlineStr">
         <is>
-          <t>Nouveau : dans l'Arène, le PNJ ouvrier est présent et son dialogue s'affiche (reconstruction en cours / Blaine au Dojo).</t>
-        </is>
-      </c>
-      <c r="D52" s="18" t="inlineStr">
-        <is>
-          <t>Nouveau</t>
-        </is>
-      </c>
+          <t>Sortir de chaque bâtiment ramène bien sur Cinnabar (pas sur l'ancien Kanto inerte).</t>
+        </is>
+      </c>
+      <c r="D52" s="18" t="inlineStr"/>
       <c r="E52" s="16" t="inlineStr">
         <is>
           <t>Non testé</t>
@@ -2425,12 +2425,12 @@
       </c>
       <c r="C53" s="17" t="inlineStr">
         <is>
-          <t>Nouveau : dans le Labo, la PNJ assistante est présente et son dialogue s'affiche (recherches au ralenti).</t>
+          <t>Ne pas entrer dans le Centre Pokémon dans ce build de test : ça déclenche le script d'attaque de l'Acte I, hors périmètre de ce test précis.</t>
         </is>
       </c>
       <c r="D53" s="18" t="inlineStr">
         <is>
-          <t>Nouveau</t>
+          <t>Ne pas entrer dans le Centre Pokémon dans ce build de test</t>
         </is>
       </c>
       <c r="E53" s="16" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="C54" s="17" t="inlineStr">
         <is>
-          <t>Nouveau : dans le Manoir, les 2 panneaux « carnet de Blaine » sont trouvables et affichent chacun un texte différent.</t>
+          <t>Nouveau : dans l'Arène, le PNJ ouvrier est présent et son dialogue s'affiche (reconstruction en cours / Blaine au Dojo).</t>
         </is>
       </c>
       <c r="D54" s="18" t="inlineStr">
@@ -2472,17 +2472,17 @@
       </c>
       <c r="B55" s="17" t="inlineStr">
         <is>
-          <t>13. Acte III — les 3 lieutenants</t>
+          <t>12. Portes de Cinnabar (Arène/Manoir/Labo) — build séparé</t>
         </is>
       </c>
       <c r="C55" s="17" t="inlineStr">
         <is>
-          <t>Lyre (Forêt de Jade) : en traversant la forêt (entre Argenta et Jadielle), une dresseuse LYRE (sprite Team Rocket) approche automatiquement et lance un combat. Dialogue d'avant-combat, de défaite et d'après-victoire s'affichent correctement.</t>
+          <t>Nouveau : dans le Labo, la PNJ assistante est présente et son dialogue s'affiche (recherches au ralenti).</t>
         </is>
       </c>
       <c r="D55" s="18" t="inlineStr">
         <is>
-          <t>Lyre</t>
+          <t>Nouveau</t>
         </is>
       </c>
       <c r="E55" s="16" t="inlineStr">
@@ -2498,17 +2498,17 @@
       </c>
       <c r="B56" s="17" t="inlineStr">
         <is>
-          <t>13. Acte III — les 3 lieutenants</t>
+          <t>12. Portes de Cinnabar (Arène/Manoir/Labo) — build séparé</t>
         </is>
       </c>
       <c r="C56" s="17" t="inlineStr">
         <is>
-          <t>Selen (Mont Sélénite) : au milieu du groupe de Clefairy sur MtMoon_Outside_hns, une dresseuse SELEN approche automatiquement et lance un combat. Mêmes vérifications (avant/défaite/après).</t>
+          <t>Nouveau : dans le Manoir, les 2 panneaux « carnet de Blaine » sont trouvables et affichent chacun un texte différent.</t>
         </is>
       </c>
       <c r="D56" s="18" t="inlineStr">
         <is>
-          <t>Selen</t>
+          <t>Nouveau</t>
         </is>
       </c>
       <c r="E56" s="16" t="inlineStr">
@@ -2529,12 +2529,12 @@
       </c>
       <c r="C57" s="17" t="inlineStr">
         <is>
-          <t>Terrence (Rock Tunnel 1F) : PNJ immobile, à aborder (pas d'approche automatique). Dérouler la séquence de 3 questions à choix multiples.</t>
+          <t>Lyre (Forêt de Jade) : en traversant la forêt (entre Argenta et Jadielle), une dresseuse LYRE (sprite Team Rocket) approche automatiquement et lance un combat. Dialogue d'avant-combat, de défaite et d'après-victoire s'affichent correctement.</t>
         </is>
       </c>
       <c r="D57" s="18" t="inlineStr">
         <is>
-          <t>Terrence</t>
+          <t>Lyre</t>
         </is>
       </c>
       <c r="E57" s="16" t="inlineStr">
@@ -2555,10 +2555,14 @@
       </c>
       <c r="C58" s="17" t="inlineStr">
         <is>
-          <t>Terrence — répondre B/A/A (le plus convaincant à chaque fois) → devrait mener à « convaincu », pas de combat, Terrence rejoint votre cause.</t>
-        </is>
-      </c>
-      <c r="D58" s="18" t="inlineStr"/>
+          <t>Selen (Mont Sélénite) : au milieu du groupe de Clefairy sur MtMoon_Outside_hns, une dresseuse SELEN approche automatiquement et lance un combat. Mêmes vérifications (avant/défaite/après).</t>
+        </is>
+      </c>
+      <c r="D58" s="18" t="inlineStr">
+        <is>
+          <t>Selen</t>
+        </is>
+      </c>
       <c r="E58" s="16" t="inlineStr">
         <is>
           <t>Non testé</t>
@@ -2577,10 +2581,14 @@
       </c>
       <c r="C59" s="17" t="inlineStr">
         <is>
-          <t>Terrence — réessayer en répondant C à la question 1 (agressif) → devrait court-circuiter directement vers un combat complet, sans poser les questions 2 et 3.</t>
-        </is>
-      </c>
-      <c r="D59" s="18" t="inlineStr"/>
+          <t>Terrence (Rock Tunnel 1F) : PNJ immobile, à aborder (pas d'approche automatique). Dérouler la séquence de 3 questions à choix multiples.</t>
+        </is>
+      </c>
+      <c r="D59" s="18" t="inlineStr">
+        <is>
+          <t>Terrence</t>
+        </is>
+      </c>
       <c r="E59" s="16" t="inlineStr">
         <is>
           <t>Non testé</t>
@@ -2599,7 +2607,7 @@
       </c>
       <c r="C60" s="17" t="inlineStr">
         <is>
-          <t>Terrence — réessayer en visant un score intermédiaire (ex. B/B/A) → devrait mener à un combat allégé (équipe réduite à 2 Pokémon, sans objets tenus) plutôt que l'équipe complète à 4.</t>
+          <t>Terrence — répondre B/A/A (le plus convaincant à chaque fois) → devrait mener à « convaincu », pas de combat, Terrence rejoint votre cause.</t>
         </is>
       </c>
       <c r="D60" s="18" t="inlineStr"/>
@@ -2621,14 +2629,10 @@
       </c>
       <c r="C61" s="17" t="inlineStr">
         <is>
-          <t>Terrence — après une défaite (quelle que soit la branche combat), reparler à Terrence : la séquence de questions ne doit pas se rejouer, le jeu doit relancer directement le même combat.</t>
-        </is>
-      </c>
-      <c r="D61" s="18" t="inlineStr">
-        <is>
-          <t>Terrence — après une défaite</t>
-        </is>
-      </c>
+          <t>Terrence — réessayer en répondant C à la question 1 (agressif) → devrait court-circuiter directement vers un combat complet, sans poser les questions 2 et 3.</t>
+        </is>
+      </c>
+      <c r="D61" s="18" t="inlineStr"/>
       <c r="E61" s="16" t="inlineStr">
         <is>
           <t>Non testé</t>
@@ -2647,14 +2651,10 @@
       </c>
       <c r="C62" s="17" t="inlineStr">
         <is>
-          <t>Pour les 3 : vérifier qu'aucun des 3 lieutenants ne bloque le passage ou ne casse le déplacement après le combat.</t>
-        </is>
-      </c>
-      <c r="D62" s="18" t="inlineStr">
-        <is>
-          <t>Pour les 3</t>
-        </is>
-      </c>
+          <t>Terrence — réessayer en visant un score intermédiaire (ex. B/B/A) → devrait mener à un combat allégé (équipe réduite à 2 Pokémon, sans objets tenus) plutôt que l'équipe complète à 4.</t>
+        </is>
+      </c>
+      <c r="D62" s="18" t="inlineStr"/>
       <c r="E62" s="16" t="inlineStr">
         <is>
           <t>Non testé</t>
@@ -2668,17 +2668,17 @@
       </c>
       <c r="B63" s="17" t="inlineStr">
         <is>
-          <t>14. Acte IV — 3 Championnes ralliées</t>
+          <t>13. Acte III — les 3 lieutenants</t>
         </is>
       </c>
       <c r="C63" s="17" t="inlineStr">
         <is>
-          <t>Erika (Céladopole) : avant le combat, un dialogue de doute en français s'affiche (méfiance envers une Championne qui a perdu son île), puis le dialogue anglais d'origine, puis le combat. Équipe niveau ~34 (pas 60+).</t>
+          <t>Terrence — après une défaite (quelle que soit la branche combat), reparler à Terrence : la séquence de questions ne doit pas se rejouer, le jeu doit relancer directement le même combat.</t>
         </is>
       </c>
       <c r="D63" s="18" t="inlineStr">
         <is>
-          <t>Erika</t>
+          <t>Terrence — après une défaite</t>
         </is>
       </c>
       <c r="E63" s="16" t="inlineStr">
@@ -2694,17 +2694,17 @@
       </c>
       <c r="B64" s="17" t="inlineStr">
         <is>
-          <t>14. Acte IV — 3 Championnes ralliées</t>
+          <t>13. Acte III — les 3 lieutenants</t>
         </is>
       </c>
       <c r="C64" s="17" t="inlineStr">
         <is>
-          <t>Sabrina (Safrania) : même schéma (doute FR → dialogue original → combat), équipe niveau ~34.</t>
+          <t>Pour les 3 : vérifier qu'aucun des 3 lieutenants ne bloque le passage ou ne casse le déplacement après le combat.</t>
         </is>
       </c>
       <c r="D64" s="18" t="inlineStr">
         <is>
-          <t>Sabrina</t>
+          <t>Pour les 3</t>
         </is>
       </c>
       <c r="E64" s="16" t="inlineStr">
@@ -2725,12 +2725,12 @@
       </c>
       <c r="C65" s="17" t="inlineStr">
         <is>
-          <t>Janine (Fuchsia) : même schéma, son dialogue de doute mentionne son père Koga. Équipe niveau ~34.</t>
+          <t>Erika (Céladopole) : avant le combat, un dialogue de doute en français s'affiche (méfiance envers une Championne qui a perdu son île), puis le dialogue anglais d'origine, puis le combat. Équipe niveau ~34 (pas 60+).</t>
         </is>
       </c>
       <c r="D65" s="18" t="inlineStr">
         <is>
-          <t>Janine</t>
+          <t>Erika</t>
         </is>
       </c>
       <c r="E65" s="16" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="C66" s="17" t="inlineStr">
         <is>
-          <t>Pour les 3 : les dresseurs élèves rencontrés avant la Championne sont aussi niveau ~34, pas surclassés.</t>
+          <t>Sabrina (Safrania) : même schéma (doute FR → dialogue original → combat), équipe niveau ~34.</t>
         </is>
       </c>
       <c r="D66" s="18" t="inlineStr">
         <is>
-          <t>Pour les 3</t>
+          <t>Sabrina</t>
         </is>
       </c>
       <c r="E66" s="16" t="inlineStr">
@@ -2777,10 +2777,14 @@
       </c>
       <c r="C67" s="17" t="inlineStr">
         <is>
-          <t>Badge reçu normalement après chaque victoire (Erika, Sabrina, Janine).</t>
-        </is>
-      </c>
-      <c r="D67" s="18" t="inlineStr"/>
+          <t>Janine (Fuchsia) : même schéma, son dialogue de doute mentionne son père Koga. Équipe niveau ~34.</t>
+        </is>
+      </c>
+      <c r="D67" s="18" t="inlineStr">
+        <is>
+          <t>Janine</t>
+        </is>
+      </c>
       <c r="E67" s="16" t="inlineStr">
         <is>
           <t>Non testé</t>
@@ -2794,15 +2798,19 @@
       </c>
       <c r="B68" s="17" t="inlineStr">
         <is>
-          <t>15. 7e Arène : retrouvailles avec Blaine (Seafoam)</t>
+          <t>14. Acte IV — 3 Championnes ralliées</t>
         </is>
       </c>
       <c r="C68" s="17" t="inlineStr">
         <is>
-          <t>Avant le combat, une scène de retrouvailles en français s'affiche (Blaine reconnaît le joueur, explique avoir été emmené ici après l'attaque de Cinnabar), puis le dialogue anglais d'origine, puis le combat.</t>
-        </is>
-      </c>
-      <c r="D68" s="18" t="inlineStr"/>
+          <t>Pour les 3 : les dresseurs élèves rencontrés avant la Championne sont aussi niveau ~34, pas surclassés.</t>
+        </is>
+      </c>
+      <c r="D68" s="18" t="inlineStr">
+        <is>
+          <t>Pour les 3</t>
+        </is>
+      </c>
       <c r="E68" s="16" t="inlineStr">
         <is>
           <t>Non testé</t>
@@ -2816,12 +2824,12 @@
       </c>
       <c r="B69" s="17" t="inlineStr">
         <is>
-          <t>15. 7e Arène : retrouvailles avec Blaine (Seafoam)</t>
+          <t>14. Acte IV — 3 Championnes ralliées</t>
         </is>
       </c>
       <c r="C69" s="17" t="inlineStr">
         <is>
-          <t>Équipe de Blaine niveau ~34 (pas 65+).</t>
+          <t>Badge reçu normalement après chaque victoire (Erika, Sabrina, Janine).</t>
         </is>
       </c>
       <c r="D69" s="18" t="inlineStr"/>
@@ -2843,7 +2851,7 @@
       </c>
       <c r="C70" s="17" t="inlineStr">
         <is>
-          <t>Badge reçu normalement après victoire.</t>
+          <t>Avant le combat, une scène de retrouvailles en français s'affiche (Blaine reconnaît le joueur, explique avoir été emmené ici après l'attaque de Cinnabar), puis le dialogue anglais d'origine, puis le combat.</t>
         </is>
       </c>
       <c r="D70" s="18" t="inlineStr"/>
@@ -2865,14 +2873,10 @@
       </c>
       <c r="C71" s="17" t="inlineStr">
         <is>
-          <t>En reparlant à Blaine après la victoire (ou en revenant plus tard) : le texte anglais d'origine s'affiche, suivi d'une ligne française (« On rentre à Cinnabar dès que possible »).</t>
-        </is>
-      </c>
-      <c r="D71" s="18" t="inlineStr">
-        <is>
-          <t>En reparlant à Blaine après la victoire</t>
-        </is>
-      </c>
+          <t>Équipe de Blaine niveau ~34 (pas 65+).</t>
+        </is>
+      </c>
+      <c r="D71" s="18" t="inlineStr"/>
       <c r="E71" s="16" t="inlineStr">
         <is>
           <t>Non testé</t>
@@ -2886,19 +2890,15 @@
       </c>
       <c r="B72" s="17" t="inlineStr">
         <is>
-          <t>16. Fin du scénario — Kess, Mira Voss, Blue, épilogue</t>
+          <t>15. 7e Arène : retrouvailles avec Blaine (Seafoam)</t>
         </is>
       </c>
       <c r="C72" s="17" t="inlineStr">
         <is>
-          <t>Kess (Zone Safari, grotte de Fuchsia) : à aborder. Même séquence de conviction à 3 questions que Terrence (convaincue sans combat / combat allégé / combat complet selon les réponses). Après une défaite, reparler à Kess relance directement le même combat sans reposer les questions.</t>
-        </is>
-      </c>
-      <c r="D72" s="18" t="inlineStr">
-        <is>
-          <t>Kess</t>
-        </is>
-      </c>
+          <t>Badge reçu normalement après victoire.</t>
+        </is>
+      </c>
+      <c r="D72" s="18" t="inlineStr"/>
       <c r="E72" s="16" t="inlineStr">
         <is>
           <t>Non testé</t>
@@ -2912,17 +2912,17 @@
       </c>
       <c r="B73" s="17" t="inlineStr">
         <is>
-          <t>16. Fin du scénario — Kess, Mira Voss, Blue, épilogue</t>
+          <t>15. 7e Arène : retrouvailles avec Blaine (Seafoam)</t>
         </is>
       </c>
       <c r="C73" s="17" t="inlineStr">
         <is>
-          <t>Mira Voss (Silph Co, Safrania) : combat direct après un court dialogue (pas de choix), équipe niveau ~34.</t>
+          <t>En reparlant à Blaine après la victoire (ou en revenant plus tard) : le texte anglais d'origine s'affiche, suivi d'une ligne française (« On rentre à Cinnabar dès que possible »).</t>
         </is>
       </c>
       <c r="D73" s="18" t="inlineStr">
         <is>
-          <t>Mira Voss</t>
+          <t>En reparlant à Blaine après la victoire</t>
         </is>
       </c>
       <c r="E73" s="16" t="inlineStr">
@@ -2943,10 +2943,14 @@
       </c>
       <c r="C74" s="17" t="inlineStr">
         <is>
-          <t>Une fois Erika + Sabrina + Janine + Major Bob + Blaine + Mira Voss tous obtenus/vaincus : le retour à Cinnabar (Route 20/21) n'est plus bloqué, et Blue apparaît désormais à l'Arène de Viridian.</t>
-        </is>
-      </c>
-      <c r="D74" s="18" t="inlineStr"/>
+          <t>Kess (Zone Safari, grotte de Fuchsia) : à aborder. Même séquence de conviction à 3 questions que Terrence (convaincue sans combat / combat allégé / combat complet selon les réponses). Après une défaite, reparler à Kess relance directement le même combat sans reposer les questions.</t>
+        </is>
+      </c>
+      <c r="D74" s="18" t="inlineStr">
+        <is>
+          <t>Kess</t>
+        </is>
+      </c>
       <c r="E74" s="16" t="inlineStr">
         <is>
           <t>Non testé</t>
@@ -2965,12 +2969,12 @@
       </c>
       <c r="C75" s="17" t="inlineStr">
         <is>
-          <t>Blue (Arène de Viridian, 8e badge) : dialogue de révélation, puis 3 questions à choix multiples, puis le dialogue anglais d'origine, puis le combat. Perdre puis retenter doit rejouer toute la séquence de dialogue.</t>
+          <t>Mira Voss (Silph Co, Safrania) : combat direct après un court dialogue (pas de choix), équipe niveau ~34.</t>
         </is>
       </c>
       <c r="D75" s="18" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>Mira Voss</t>
         </is>
       </c>
       <c r="E75" s="16" t="inlineStr">
@@ -2991,14 +2995,10 @@
       </c>
       <c r="C76" s="17" t="inlineStr">
         <is>
-          <t>Juste après la victoire sur Blue : un épilogue en français s'affiche automatiquement (3 variantes selon la réputation accumulée — ternie/équilibrée/exemplaire). Vérifier qu'il ne se rejoue pas en revenant à l'Arène plus tard.</t>
-        </is>
-      </c>
-      <c r="D76" s="18" t="inlineStr">
-        <is>
-          <t>Juste après la victoire sur Blue</t>
-        </is>
-      </c>
+          <t>Une fois Erika + Sabrina + Janine + Major Bob + Blaine + Mira Voss tous obtenus/vaincus : le retour à Cinnabar (Route 20/21) n'est plus bloqué, et Blue apparaît désormais à l'Arène de Viridian.</t>
+        </is>
+      </c>
+      <c r="D76" s="18" t="inlineStr"/>
       <c r="E76" s="16" t="inlineStr">
         <is>
           <t>Non testé</t>
@@ -3017,12 +3017,12 @@
       </c>
       <c r="C77" s="17" t="inlineStr">
         <is>
-          <t>Si l'épilogue « exemplaire » s'affiche : vérifier que le texte mentionne un accès aux sous-sols du Pokémon Mansion (contenu réel non encore implémenté — normal que rien de plus ne se passe pour l'instant).</t>
+          <t>Blue (Arène de Viridian, 8e badge) : dialogue de révélation, puis 3 questions à choix multiples, puis le dialogue anglais d'origine, puis le combat. Perdre puis retenter doit rejouer toute la séquence de dialogue.</t>
         </is>
       </c>
       <c r="D77" s="18" t="inlineStr">
         <is>
-          <t>Si l'épilogue « exemplaire » s'affiche</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="E77" s="16" t="inlineStr">
@@ -3038,15 +3038,19 @@
       </c>
       <c r="B78" s="17" t="inlineStr">
         <is>
-          <t>17. Les 8 aspirants Champions (rencontres aléatoires)</t>
+          <t>16. Fin du scénario — Kess, Mira Voss, Blue, épilogue</t>
         </is>
       </c>
       <c r="C78" s="17" t="inlineStr">
         <is>
-          <t>Sur Route21_hns, ViridianForest_hns, Route15_hns, SeafoamIslands_1F_hns, Route1_hns, RockTunnel_1F_hns et CeladonCity_hns : en traversant la zone plusieurs fois (1 chance sur 20 par visite), un dresseur aspirant apparaît parfois là où il n'y avait rien avant.</t>
-        </is>
-      </c>
-      <c r="D78" s="18" t="inlineStr"/>
+          <t>Juste après la victoire sur Blue : un épilogue en français s'affiche automatiquement (3 variantes selon la réputation accumulée — ternie/équilibrée/exemplaire). Vérifier qu'il ne se rejoue pas en revenant à l'Arène plus tard.</t>
+        </is>
+      </c>
+      <c r="D78" s="18" t="inlineStr">
+        <is>
+          <t>Juste après la victoire sur Blue</t>
+        </is>
+      </c>
       <c r="E78" s="16" t="inlineStr">
         <is>
           <t>Non testé</t>
@@ -3060,15 +3064,19 @@
       </c>
       <c r="B79" s="17" t="inlineStr">
         <is>
-          <t>17. Les 8 aspirants Champions (rencontres aléatoires)</t>
+          <t>16. Fin du scénario — Kess, Mira Voss, Blue, épilogue</t>
         </is>
       </c>
       <c r="C79" s="17" t="inlineStr">
         <is>
-          <t>Chaque aspirant a un dialogue d'avant-combat, de défaite et d'après-victoire propre (pas de texte générique/dupliqué entre deux aspirants).</t>
-        </is>
-      </c>
-      <c r="D79" s="18" t="inlineStr"/>
+          <t>Si l'épilogue « exemplaire » s'affiche : vérifier que le texte mentionne un accès aux sous-sols du Pokémon Mansion (contenu réel non encore implémenté — normal que rien de plus ne se passe pour l'instant).</t>
+        </is>
+      </c>
+      <c r="D79" s="18" t="inlineStr">
+        <is>
+          <t>Si l'épilogue « exemplaire » s'affiche</t>
+        </is>
+      </c>
       <c r="E79" s="16" t="inlineStr">
         <is>
           <t>Non testé</t>
@@ -3087,14 +3095,10 @@
       </c>
       <c r="C80" s="17" t="inlineStr">
         <is>
-          <t>Corvin (Route 1) : ne doit apparaître que de nuit (vérifier avec l'horloge de la console — ne pas le chercher en plein jour).</t>
-        </is>
-      </c>
-      <c r="D80" s="18" t="inlineStr">
-        <is>
-          <t>Corvin</t>
-        </is>
-      </c>
+          <t>Sur Route21_hns, ViridianForest_hns, Route15_hns, SeafoamIslands_1F_hns, Route1_hns, RockTunnel_1F_hns et CeladonCity_hns : en traversant la zone plusieurs fois (1 chance sur 20 par visite), un dresseur aspirant apparaît parfois là où il n'y avait rien avant.</t>
+        </is>
+      </c>
+      <c r="D80" s="18" t="inlineStr"/>
       <c r="E80" s="16" t="inlineStr">
         <is>
           <t>Non testé</t>
@@ -3113,14 +3117,10 @@
       </c>
       <c r="C81" s="17" t="inlineStr">
         <is>
-          <t>Ael (Route 21, x2) et Orin (Route 21, x2) : les deux peuvent apparaître sur la même route, à des occasions différentes, sans se remplacer l'un l'autre.</t>
-        </is>
-      </c>
-      <c r="D81" s="18" t="inlineStr">
-        <is>
-          <t>Ael</t>
-        </is>
-      </c>
+          <t>Chaque aspirant a un dialogue d'avant-combat, de défaite et d'après-victoire propre (pas de texte générique/dupliqué entre deux aspirants).</t>
+        </is>
+      </c>
+      <c r="D81" s="18" t="inlineStr"/>
       <c r="E81" s="16" t="inlineStr">
         <is>
           <t>Non testé</t>
@@ -3139,10 +3139,14 @@
       </c>
       <c r="C82" s="17" t="inlineStr">
         <is>
-          <t>Chaque aspirant reste rejouable à une rencontre aléatoire ultérieure (pas de disparition définitive après une victoire — simplification voulue et documentée).</t>
-        </is>
-      </c>
-      <c r="D82" s="18" t="inlineStr"/>
+          <t>Corvin (Route 1) : ne doit apparaître que de nuit (vérifier avec l'horloge de la console — ne pas le chercher en plein jour).</t>
+        </is>
+      </c>
+      <c r="D82" s="18" t="inlineStr">
+        <is>
+          <t>Corvin</t>
+        </is>
+      </c>
       <c r="E82" s="16" t="inlineStr">
         <is>
           <t>Non testé</t>
@@ -3161,10 +3165,14 @@
       </c>
       <c r="C83" s="17" t="inlineStr">
         <is>
-          <t>En battant au moins 6 des 8 aspirants sur la partie, puis en terminant le scénario avec l'épilogue exemplaire : un texte additionnel dédié aux aspirants doit s'afficher à la suite de l'épilogue normal.</t>
-        </is>
-      </c>
-      <c r="D83" s="18" t="inlineStr"/>
+          <t>Ael (Route 21, x2) et Orin (Route 21, x2) : les deux peuvent apparaître sur la même route, à des occasions différentes, sans se remplacer l'un l'autre.</t>
+        </is>
+      </c>
+      <c r="D83" s="18" t="inlineStr">
+        <is>
+          <t>Ael</t>
+        </is>
+      </c>
       <c r="E83" s="16" t="inlineStr">
         <is>
           <t>Non testé</t>
@@ -3178,19 +3186,15 @@
       </c>
       <c r="B84" s="17" t="inlineStr">
         <is>
-          <t>18. Les 18 événements narratifs supplémentaires</t>
+          <t>17. Les 8 aspirants Champions (rencontres aléatoires)</t>
         </is>
       </c>
       <c r="C84" s="17" t="inlineStr">
         <is>
-          <t>Acte I : 4 nouveaux moments s'intercalent dans les scènes déjà connues de la chute de Cinnabar (choix de sauvetage, carnet du grunt trouvé, choix pour un Pokémon blessé, scène avec un marin sur la Route 21 pendant la tempête) — aucun ne doit bloquer la progression.</t>
-        </is>
-      </c>
-      <c r="D84" s="18" t="inlineStr">
-        <is>
-          <t>Acte I</t>
-        </is>
-      </c>
+          <t>Chaque aspirant reste rejouable à une rencontre aléatoire ultérieure (pas de disparition définitive après une victoire — simplification voulue et documentée).</t>
+        </is>
+      </c>
+      <c r="D84" s="18" t="inlineStr"/>
       <c r="E84" s="16" t="inlineStr">
         <is>
           <t>Non testé</t>
@@ -3204,19 +3208,15 @@
       </c>
       <c r="B85" s="17" t="inlineStr">
         <is>
-          <t>18. Les 18 événements narratifs supplémentaires</t>
+          <t>17. Les 8 aspirants Champions (rencontres aléatoires)</t>
         </is>
       </c>
       <c r="C85" s="17" t="inlineStr">
         <is>
-          <t>Acte II : à Jadielle, le jeune dresseur croisé près du Bourg Palette a une ligne de dialogue supplémentaire ; à Argenta, le commerçant a une ligne après le discours de Blue entendu à la radio/en ville.</t>
-        </is>
-      </c>
-      <c r="D85" s="18" t="inlineStr">
-        <is>
-          <t>Acte II</t>
-        </is>
-      </c>
+          <t>En battant au moins 6 des 8 aspirants sur la partie, puis en terminant le scénario avec l'épilogue exemplaire : un texte additionnel dédié aux aspirants doit s'afficher à la suite de l'épilogue normal.</t>
+        </is>
+      </c>
+      <c r="D85" s="18" t="inlineStr"/>
       <c r="E85" s="16" t="inlineStr">
         <is>
           <t>Non testé</t>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="C86" s="17" t="inlineStr">
         <is>
-          <t>Pewter (panneau photo) : près du marché, un panneau invisible (marcher dessus + A) affiche un vieux cliché de Blaine jeune avec une dresseuse qui ressemble au joueur — uniquement visible après l'Acte I.</t>
+          <t>Acte I : 4 nouveaux moments s'intercalent dans les scènes déjà connues de la chute de Cinnabar (choix de sauvetage, carnet du grunt trouvé, choix pour un Pokémon blessé, scène avec un marin sur la Route 21 pendant la tempête) — aucun ne doit bloquer la progression.</t>
         </is>
       </c>
       <c r="D86" s="18" t="inlineStr">
         <is>
-          <t>Pewter</t>
+          <t>Acte I</t>
         </is>
       </c>
       <c r="E86" s="16" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="C87" s="17" t="inlineStr">
         <is>
-          <t>Route 3 (patrouille de reconnaissance) : entre Jadielle et le Mont Sélénite, un Grunt Rocket isolé lance un combat mineur, avant les vrais lieutenants de l'Acte III.</t>
+          <t>Acte II : à Jadielle, le jeune dresseur croisé près du Bourg Palette a une ligne de dialogue supplémentaire ; à Argenta, le commerçant a une ligne après le discours de Blue entendu à la radio/en ville.</t>
         </is>
       </c>
       <c r="D87" s="18" t="inlineStr">
         <is>
-          <t>Route 3</t>
+          <t>Acte II</t>
         </is>
       </c>
       <c r="E87" s="16" t="inlineStr">
@@ -3287,12 +3287,12 @@
       </c>
       <c r="C88" s="17" t="inlineStr">
         <is>
-          <t>Mont Sélénite : fragments de folklore Clefairy déjà présents dans le jeu de base, visibles avant/pendant la scène avec Selen (rien de nouveau à vérifier au-delà de l'existant).</t>
+          <t>Pewter (panneau photo) : près du marché, un panneau invisible (marcher dessus + A) affiche un vieux cliché de Blaine jeune avec une dresseuse qui ressemble au joueur — uniquement visible après l'Acte I.</t>
         </is>
       </c>
       <c r="D88" s="18" t="inlineStr">
         <is>
-          <t>Mont Sélénite</t>
+          <t>Pewter</t>
         </is>
       </c>
       <c r="E88" s="16" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="C89" s="17" t="inlineStr">
         <is>
-          <t>Capture d'un Champion allié : au fil de l'Acte III, une ligne de texte évoque la capture brève d'un Champion déjà rallié (Pierre ou Ondine) par la Team Rocket.</t>
+          <t>Route 3 (patrouille de reconnaissance) : entre Jadielle et le Mont Sélénite, un Grunt Rocket isolé lance un combat mineur, avant les vrais lieutenants de l'Acte III.</t>
         </is>
       </c>
       <c r="D89" s="18" t="inlineStr">
         <is>
-          <t>Capture d'un Champion allié</t>
+          <t>Route 3</t>
         </is>
       </c>
       <c r="E89" s="16" t="inlineStr">
@@ -3339,12 +3339,12 @@
       </c>
       <c r="C90" s="17" t="inlineStr">
         <is>
-          <t>Terrence (éboulement du Rock Tunnel) : juste avant la séquence de conviction, un texte d'éboulement/alliance temporaire s'affiche avant les 3 questions habituelles.</t>
+          <t>Mont Sélénite : fragments de folklore Clefairy déjà présents dans le jeu de base, visibles avant/pendant la scène avec Selen (rien de nouveau à vérifier au-delà de l'existant).</t>
         </is>
       </c>
       <c r="D90" s="18" t="inlineStr">
         <is>
-          <t>Terrence</t>
+          <t>Mont Sélénite</t>
         </is>
       </c>
       <c r="E90" s="16" t="inlineStr">
@@ -3365,12 +3365,12 @@
       </c>
       <c r="C91" s="17" t="inlineStr">
         <is>
-          <t>Kess (labo caché de la Zone Safari) : juste avant la séquence de conviction, un texte décrit d'anciennes installations d'expérimentation portant le sceau de Giovanni.</t>
+          <t>Capture d'un Champion allié : au fil de l'Acte III, une ligne de texte évoque la capture brève d'un Champion déjà rallié (Pierre ou Ondine) par la Team Rocket.</t>
         </is>
       </c>
       <c r="D91" s="18" t="inlineStr">
         <is>
-          <t>Kess</t>
+          <t>Capture d'un Champion allié</t>
         </is>
       </c>
       <c r="E91" s="16" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="C92" s="17" t="inlineStr">
         <is>
-          <t>Céladopole (subordonné admiratif) : un dresseur optionnel, convaincu par le discours de Blue mais pas violent, propose un combat facultatif ; sa défaite montre un doute dans son texte d'après-combat.</t>
+          <t>Terrence (éboulement du Rock Tunnel) : juste avant la séquence de conviction, un texte d'éboulement/alliance temporaire s'affiche avant les 3 questions habituelles.</t>
         </is>
       </c>
       <c r="D92" s="18" t="inlineStr">
         <is>
-          <t>Céladopole</t>
+          <t>Terrence</t>
         </is>
       </c>
       <c r="E92" s="16" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="C93" s="17" t="inlineStr">
         <is>
-          <t>Janine (scission du clan) : juste après avoir obtenu le badge de Fuchsia, un texte supplémentaire évoque une tentative de sabotage isolée par une minorité du clan, déjà réglée — ne doit apparaître qu'une seule fois.</t>
+          <t>Kess (labo caché de la Zone Safari) : juste avant la séquence de conviction, un texte décrit d'anciennes installations d'expérimentation portant le sceau de Giovanni.</t>
         </is>
       </c>
       <c r="D93" s="18" t="inlineStr">
         <is>
-          <t>Janine</t>
+          <t>Kess</t>
         </is>
       </c>
       <c r="E93" s="16" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="C94" s="17" t="inlineStr">
         <is>
-          <t>Silph Co (piste de Blaine + alarme) : juste avant le combat contre Mira Voss, deux textes s'affichent dans l'ordre — un registre de détention au nom de Blaine (déjà retrouvé), puis une alarme dans les étages supérieurs.</t>
+          <t>Céladopole (subordonné admiratif) : un dresseur optionnel, convaincu par le discours de Blue mais pas violent, propose un combat facultatif ; sa défaite montre un doute dans son texte d'après-combat.</t>
         </is>
       </c>
       <c r="D94" s="18" t="inlineStr">
         <is>
-          <t>Silph Co</t>
+          <t>Céladopole</t>
         </is>
       </c>
       <c r="E94" s="16" t="inlineStr">
@@ -3469,12 +3469,12 @@
       </c>
       <c r="C95" s="17" t="inlineStr">
         <is>
-          <t>Retrouvailles avec Blaine (Seafoam) : déjà couvert par la section 15 de cette liste — pas de nouveau point à tester ici.</t>
+          <t>Janine (scission du clan) : juste après avoir obtenu le badge de Fuchsia, un texte supplémentaire évoque une tentative de sabotage isolée par une minorité du clan, déjà réglée — ne doit apparaître qu'une seule fois.</t>
         </is>
       </c>
       <c r="D95" s="18" t="inlineStr">
         <is>
-          <t>Retrouvailles avec Blaine</t>
+          <t>Janine</t>
         </is>
       </c>
       <c r="E95" s="16" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="C96" s="17" t="inlineStr">
         <is>
-          <t>Retour des alliés (avant Blue) : juste avant la révélation de Blue à l'Arène de Viridian, un texte récapitule les Champions ralliés — varie selon Terrence/Kess convaincus, puis une seconde ligne selon le débat du clan de Fuchsia (section 19). Une seule fois, même après une défaite contre Blue.</t>
+          <t>Silph Co (piste de Blaine + alarme) : juste avant le combat contre Mira Voss, deux textes s'affichent dans l'ordre — un registre de détention au nom de Blaine (déjà retrouvé), puis une alarme dans les étages supérieurs.</t>
         </is>
       </c>
       <c r="D96" s="18" t="inlineStr">
         <is>
-          <t>Retour des alliés</t>
+          <t>Silph Co</t>
         </is>
       </c>
       <c r="E96" s="16" t="inlineStr">
@@ -3516,17 +3516,17 @@
       </c>
       <c r="B97" s="17" t="inlineStr">
         <is>
-          <t>19. Les 3 histoires secondaires restantes (section 8)</t>
+          <t>18. Les 18 événements narratifs supplémentaires</t>
         </is>
       </c>
       <c r="C97" s="17" t="inlineStr">
         <is>
-          <t>Fuchsia (débat du clan) : en entrant dans l'Arène pour la première fois (après l'Acte II), avant le dialogue de doute habituel de Janine, un texte présente le clan divisé (engagement direct / stratégie de l'ombre) puis propose un choix. Ne doit se jouer qu'une seule fois.</t>
+          <t>Retrouvailles avec Blaine (Seafoam) : déjà couvert par la section 15 de cette liste — pas de nouveau point à tester ici.</t>
         </is>
       </c>
       <c r="D97" s="18" t="inlineStr">
         <is>
-          <t>Fuchsia</t>
+          <t>Retrouvailles avec Blaine</t>
         </is>
       </c>
       <c r="E97" s="16" t="inlineStr">
@@ -3542,15 +3542,19 @@
       </c>
       <c r="B98" s="17" t="inlineStr">
         <is>
-          <t>19. Les 3 histoires secondaires restantes (section 8)</t>
+          <t>18. Les 18 événements narratifs supplémentaires</t>
         </is>
       </c>
       <c r="C98" s="17" t="inlineStr">
         <is>
-          <t>Le choix fait à Fuchsia influence la ligne additionnelle de la scène « retour des alliés » avant Blue (section 18) : ninjas visibles si « engagement direct », surveillance discrète si « stratégie de l'ombre ».</t>
-        </is>
-      </c>
-      <c r="D98" s="18" t="inlineStr"/>
+          <t>Retour des alliés (avant Blue) : juste avant la révélation de Blue à l'Arène de Viridian, un texte récapitule les Champions ralliés — varie selon Terrence/Kess convaincus, puis une seconde ligne selon le débat du clan de Fuchsia (section 19). Une seule fois, même après une défaite contre Blue.</t>
+        </is>
+      </c>
+      <c r="D98" s="18" t="inlineStr">
+        <is>
+          <t>Retour des alliés</t>
+        </is>
+      </c>
       <c r="E98" s="16" t="inlineStr">
         <is>
           <t>Non testé</t>
@@ -3569,12 +3573,12 @@
       </c>
       <c r="C99" s="17" t="inlineStr">
         <is>
-          <t>Céladopole (financement Rocket) : dans le grand magasin (rez-de-chaussée), un panneau invisible révèle des registres de comptes qui ne correspondent pas aux ventes officielles — optionnel, ne bloque rien.</t>
+          <t>Fuchsia (débat du clan) : en entrant dans l'Arène pour la première fois (après l'Acte II), avant le dialogue de doute habituel de Janine, un texte présente le clan divisé (engagement direct / stratégie de l'ombre) puis propose un choix. Ne doit se jouer qu'une seule fois.</t>
         </is>
       </c>
       <c r="D99" s="18" t="inlineStr">
         <is>
-          <t>Céladopole</t>
+          <t>Fuchsia</t>
         </is>
       </c>
       <c r="E99" s="16" t="inlineStr">
@@ -3595,14 +3599,10 @@
       </c>
       <c r="C100" s="17" t="inlineStr">
         <is>
-          <t>Si ce panneau a été trouvé avant de battre Erika : une ligne de remerciement supplémentaire s'affiche juste après la victoire. Si non trouvé, rien ne change dans la scène d'Erika.</t>
-        </is>
-      </c>
-      <c r="D100" s="18" t="inlineStr">
-        <is>
-          <t>Si ce panneau a été trouvé avant de battre Erika</t>
-        </is>
-      </c>
+          <t>Le choix fait à Fuchsia influence la ligne additionnelle de la scène « retour des alliés » avant Blue (section 18) : ninjas visibles si « engagement direct », surveillance discrète si « stratégie de l'ombre ».</t>
+        </is>
+      </c>
+      <c r="D100" s="18" t="inlineStr"/>
       <c r="E100" s="16" t="inlineStr">
         <is>
           <t>Non testé</t>
@@ -3621,28 +3621,80 @@
       </c>
       <c r="C101" s="17" t="inlineStr">
         <is>
+          <t>Céladopole (financement Rocket) : dans le grand magasin (rez-de-chaussée), un panneau invisible révèle des registres de comptes qui ne correspondent pas aux ventes officielles — optionnel, ne bloque rien.</t>
+        </is>
+      </c>
+      <c r="D101" s="18" t="inlineStr">
+        <is>
+          <t>Céladopole</t>
+        </is>
+      </c>
+      <c r="E101" s="16" t="inlineStr">
+        <is>
+          <t>Non testé</t>
+        </is>
+      </c>
+      <c r="F101" s="17" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="16" t="n">
+        <v>99</v>
+      </c>
+      <c r="B102" s="17" t="inlineStr">
+        <is>
+          <t>19. Les 3 histoires secondaires restantes (section 8)</t>
+        </is>
+      </c>
+      <c r="C102" s="17" t="inlineStr">
+        <is>
+          <t>Si ce panneau a été trouvé avant de battre Erika : une ligne de remerciement supplémentaire s'affiche juste après la victoire. Si non trouvé, rien ne change dans la scène d'Erika.</t>
+        </is>
+      </c>
+      <c r="D102" s="18" t="inlineStr">
+        <is>
+          <t>Si ce panneau a été trouvé avant de battre Erika</t>
+        </is>
+      </c>
+      <c r="E102" s="16" t="inlineStr">
+        <is>
+          <t>Non testé</t>
+        </is>
+      </c>
+      <c r="F102" s="17" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="16" t="n">
+        <v>100</v>
+      </c>
+      <c r="B103" s="17" t="inlineStr">
+        <is>
+          <t>19. Les 3 histoires secondaires restantes (section 8)</t>
+        </is>
+      </c>
+      <c r="C103" s="17" t="inlineStr">
+        <is>
           <t>Safrania/Silph Co (dossier de Mira Voss) : avant le combat, un panneau invisible affiche un dossier RH à son nom (réaffectation, motif « restructuration ») — texte différent de ce que Mira dit à l'oral juste après. Optionnel, ne bloque rien.</t>
         </is>
       </c>
-      <c r="D101" s="18" t="inlineStr">
+      <c r="D103" s="18" t="inlineStr">
         <is>
           <t>Safrania/Silph Co</t>
         </is>
       </c>
-      <c r="E101" s="16" t="inlineStr">
-        <is>
-          <t>Non testé</t>
-        </is>
-      </c>
-      <c r="F101" s="17" t="inlineStr"/>
+      <c r="E103" s="16" t="inlineStr">
+        <is>
+          <t>Non testé</t>
+        </is>
+      </c>
+      <c r="F103" s="17" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:F101"/>
+  <autoFilter ref="A3:F103"/>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
-  <conditionalFormatting sqref="E4:E101">
+  <conditionalFormatting sqref="E4:E103">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"OK"</formula>
     </cfRule>
@@ -3654,7 +3706,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E4:E101" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="E4:E103" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Non testé,OK,KO"</formula1>
     </dataValidation>
   </dataValidations>
